--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Беседы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Беседы/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92553354904</v>
+        <v>46157.93106440768</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Беседы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Беседы/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93106440768</v>
+        <v>46157.93132211216</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Беседы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Беседы/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93132211216</v>
+        <v>46157.93380169463</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Беседы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Беседы/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93380169463</v>
+        <v>46157.93690632668</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Беседы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Беседы/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93690632668</v>
+        <v>46158.28203191464</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Беседы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Беседы/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28203191464</v>
+        <v>46158.29734325255</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Беседы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Беседы/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29734325255</v>
+        <v>46158.29803295633</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Беседы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Беседы/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29803295633</v>
+        <v>46158.33367025128</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Беседы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Беседы/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33367025128</v>
+        <v>46158.37218926739</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Беседы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/Беседы/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37218926739</v>
+        <v>46158.3727375579</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
